--- a/data/trans_orig/P11-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P11-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según dificultad en su trabajo habitual las últimas 4 semanas por el dolor en 2007</t>
+          <t>Población según dificultad en su trabajo habitual las últimas 4 semanas por el dolor en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2539</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13811</t>
+          <t>13068</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11676</t>
+          <t>12367</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21022</t>
+          <t>21054</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6692</t>
+          <t>6905</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21197</t>
+          <t>20334</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>9442</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25019</t>
+          <t>24280</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18854</t>
+          <t>19475</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39777</t>
+          <t>39986</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29829</t>
+          <t>29283</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53265</t>
+          <t>53947</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>44845</t>
+          <t>44536</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>72031</t>
+          <t>71231</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>79792</t>
+          <t>76958</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116566</t>
+          <t>116072</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>78017</t>
+          <t>78702</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>114652</t>
+          <t>113964</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>107367</t>
+          <t>108206</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>147039</t>
+          <t>149657</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>197696</t>
+          <t>196473</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>250300</t>
+          <t>247656</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,92%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>519133</t>
+          <t>518284</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>561753</t>
+          <t>560251</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>461935</t>
+          <t>457792</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>509703</t>
+          <t>504372</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>66,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>990569</t>
+          <t>992417</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1053389</t>
+          <t>1054454</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>76,28%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4156</t>
+          <t>4776</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16794</t>
+          <t>17529</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,82 +1430,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>11982</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>6188</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>21962</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>21129</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>13749</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>33765</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>1,75%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>11982</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>5686</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>22170</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>21129</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>13100</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>33145</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20626</t>
+          <t>20454</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43061</t>
+          <t>42547</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19420</t>
+          <t>19837</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41808</t>
+          <t>41307</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>43962</t>
+          <t>44569</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>74346</t>
+          <t>74877</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32479</t>
+          <t>32580</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>59217</t>
+          <t>59290</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>51762</t>
+          <t>50783</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>82962</t>
+          <t>85676</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>89016</t>
+          <t>90883</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>132675</t>
+          <t>134382</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51985</t>
+          <t>52438</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82006</t>
+          <t>83849</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>130814</t>
+          <t>129978</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>178973</t>
+          <t>175620</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>190075</t>
+          <t>191595</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>247487</t>
+          <t>248156</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,86%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>788571</t>
+          <t>787573</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>833520</t>
+          <t>832462</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>679438</t>
+          <t>679227</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>736308</t>
+          <t>736834</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1483373</t>
+          <t>1487392</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1557450</t>
+          <t>1557767</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,71%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3636</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16555</t>
+          <t>16727</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8517</t>
+          <t>7767</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23778</t>
+          <t>22758</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15514</t>
+          <t>14759</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33707</t>
+          <t>34155</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9385</t>
+          <t>9353</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27773</t>
+          <t>28269</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>32897</t>
+          <t>32319</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>57869</t>
+          <t>58580</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>46747</t>
+          <t>46203</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>77300</t>
+          <t>78545</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18115</t>
+          <t>18638</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>37671</t>
+          <t>38729</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>41405</t>
+          <t>42999</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>69045</t>
+          <t>70156</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>65996</t>
+          <t>65034</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>102406</t>
+          <t>100956</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>64468</t>
+          <t>63551</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>107522</t>
+          <t>105427</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>148684</t>
+          <t>144970</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>178735</t>
+          <t>180568</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>233092</t>
+          <t>233548</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,14%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>524502</t>
+          <t>522729</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>567620</t>
+          <t>567470</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>415651</t>
+          <t>417810</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>467462</t>
+          <t>468274</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>61,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>957833</t>
+          <t>958422</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1023173</t>
+          <t>1024679</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>75,21%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2582</t>
+          <t>2591</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12137</t>
+          <t>12378</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13606</t>
+          <t>13999</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31957</t>
+          <t>32553</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18861</t>
+          <t>18798</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>39209</t>
+          <t>40411</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17366</t>
+          <t>17077</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>35570</t>
+          <t>38178</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24508</t>
+          <t>23714</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>48298</t>
+          <t>47543</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>44761</t>
+          <t>45803</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>76301</t>
+          <t>75402</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>21367</t>
+          <t>20504</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>41452</t>
+          <t>41924</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>62714</t>
+          <t>62290</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>97621</t>
+          <t>97584</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>89495</t>
+          <t>89935</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>130723</t>
+          <t>132452</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>82840</t>
+          <t>83343</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>120897</t>
+          <t>118808</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>125101</t>
+          <t>126184</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>170297</t>
+          <t>173002</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>218553</t>
+          <t>223245</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>279044</t>
+          <t>280865</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,18%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>756553</t>
+          <t>758342</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>802234</t>
+          <t>802231</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>727044</t>
+          <t>723424</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>782761</t>
+          <t>783592</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1499889</t>
+          <t>1497289</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1576289</t>
+          <t>1571085</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,31%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>20110</t>
+          <t>21023</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>42348</t>
+          <t>42271</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>39782</t>
+          <t>38818</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>70991</t>
+          <t>69240</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>65656</t>
+          <t>66961</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>101012</t>
+          <t>102020</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>67249</t>
+          <t>69919</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>104364</t>
+          <t>105626</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>103080</t>
+          <t>102685</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>147165</t>
+          <t>145501</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>181146</t>
+          <t>181541</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>233994</t>
+          <t>236082</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>120486</t>
+          <t>118111</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>164054</t>
+          <t>163093</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>227339</t>
+          <t>225766</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>289377</t>
+          <t>287453</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>360902</t>
+          <t>359883</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>438459</t>
+          <t>437766</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>308539</t>
+          <t>305354</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>378681</t>
+          <t>374715</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>512552</t>
+          <t>509992</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>597428</t>
+          <t>600860</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>839515</t>
+          <t>835059</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>948038</t>
+          <t>950142</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,28%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2633678</t>
+          <t>2633467</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2723560</t>
+          <t>2722206</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2342857</t>
+          <t>2336818</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2447853</t>
+          <t>2445226</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5000553</t>
+          <t>5006041</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5141367</t>
+          <t>5144842</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,3%</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según dificultad en su trabajo habitual las últimas 4 semanas por el dolor en 2012</t>
+          <t>Población según dificultad en su trabajo habitual las últimas 4 semanas por el dolor en 2012 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7852</t>
+          <t>7946</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24304</t>
+          <t>24378</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16431</t>
+          <t>17363</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38372</t>
+          <t>37374</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29361</t>
+          <t>28902</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54048</t>
+          <t>54103</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17185</t>
+          <t>17799</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38611</t>
+          <t>39092</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40018</t>
+          <t>40736</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68838</t>
+          <t>69593</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>62554</t>
+          <t>65125</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>99839</t>
+          <t>98416</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21815</t>
+          <t>21517</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>44672</t>
+          <t>43329</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>38131</t>
+          <t>38461</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>67752</t>
+          <t>65578</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>65810</t>
+          <t>65626</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>102222</t>
+          <t>102912</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45684</t>
+          <t>45322</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77688</t>
+          <t>75971</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>86371</t>
+          <t>87243</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>125437</t>
+          <t>127653</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>141626</t>
+          <t>144009</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>192332</t>
+          <t>194766</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>542928</t>
+          <t>543468</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>586053</t>
+          <t>585680</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>431606</t>
+          <t>429748</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>484343</t>
+          <t>485158</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>986246</t>
+          <t>989387</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1060276</t>
+          <t>1056008</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>71,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>75,81%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9810</t>
+          <t>9907</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26769</t>
+          <t>26938</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23286</t>
+          <t>24047</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47748</t>
+          <t>47847</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38374</t>
+          <t>38538</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67777</t>
+          <t>67154</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23617</t>
+          <t>23623</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48252</t>
+          <t>48774</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54739</t>
+          <t>54667</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>87535</t>
+          <t>90097</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>85580</t>
+          <t>84873</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>123803</t>
+          <t>124460</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25642</t>
+          <t>25322</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>50453</t>
+          <t>48758</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>50326</t>
+          <t>49843</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>82406</t>
+          <t>82020</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>82385</t>
+          <t>83573</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>123306</t>
+          <t>123433</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>101304</t>
+          <t>103516</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>145820</t>
+          <t>147023</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>132750</t>
+          <t>132426</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>180149</t>
+          <t>178769</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>244847</t>
+          <t>247600</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>310661</t>
+          <t>311163</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,23%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>774946</t>
+          <t>776945</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>829612</t>
+          <t>830707</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>673951</t>
+          <t>674993</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>735339</t>
+          <t>736529</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1469175</t>
+          <t>1467482</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1551964</t>
+          <t>1546760</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>75,68%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t>5417</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22595</t>
+          <t>21207</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16672</t>
+          <t>15695</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37936</t>
+          <t>37790</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25102</t>
+          <t>26342</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50907</t>
+          <t>50861</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11230</t>
+          <t>11292</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31430</t>
+          <t>31318</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34737</t>
+          <t>34003</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>63152</t>
+          <t>62422</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>51610</t>
+          <t>50482</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>86653</t>
+          <t>87661</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>10212</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>29480</t>
+          <t>30332</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32172</t>
+          <t>32665</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>58594</t>
+          <t>59370</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>47204</t>
+          <t>47999</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>79171</t>
+          <t>81347</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>39168</t>
+          <t>39251</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>67272</t>
+          <t>67875</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>86445</t>
+          <t>84939</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>124601</t>
+          <t>123223</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>130907</t>
+          <t>130359</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>179427</t>
+          <t>179218</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>633365</t>
+          <t>631831</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>672374</t>
+          <t>671619</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>527310</t>
+          <t>530502</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>582529</t>
+          <t>582124</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1176912</t>
+          <t>1176403</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1244526</t>
+          <t>1243414</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,18%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5902</t>
+          <t>5807</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20979</t>
+          <t>19799</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18408</t>
+          <t>18906</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39194</t>
+          <t>39364</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28094</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>53514</t>
+          <t>52915</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>27021</t>
+          <t>28411</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>53890</t>
+          <t>55628</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>51579</t>
+          <t>51734</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>84096</t>
+          <t>85183</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>85398</t>
+          <t>88317</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>128345</t>
+          <t>130496</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>25555</t>
+          <t>24245</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>50170</t>
+          <t>48887</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>68619</t>
+          <t>68830</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>104595</t>
+          <t>102446</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>99257</t>
+          <t>98507</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>143062</t>
+          <t>141102</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>93956</t>
+          <t>95125</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>136908</t>
+          <t>137321</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>130986</t>
+          <t>130262</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>178273</t>
+          <t>177641</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>237163</t>
+          <t>236979</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>302781</t>
+          <t>301638</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,11%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>717545</t>
+          <t>716927</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>771101</t>
+          <t>768250</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>687694</t>
+          <t>687864</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>752016</t>
+          <t>746734</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1421478</t>
+          <t>1418409</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1502923</t>
+          <t>1501408</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,23%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>39910</t>
+          <t>39638</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>70118</t>
+          <t>70260</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>93525</t>
+          <t>94622</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>138844</t>
+          <t>139186</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>141781</t>
+          <t>142552</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>194774</t>
+          <t>194847</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>98325</t>
+          <t>97736</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>144968</t>
+          <t>143622</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>207445</t>
+          <t>206877</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>270608</t>
+          <t>267523</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>318179</t>
+          <t>320164</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>394231</t>
+          <t>397484</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>99118</t>
+          <t>100001</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>144022</t>
+          <t>142744</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>217048</t>
+          <t>214295</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>283235</t>
+          <t>277515</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>329667</t>
+          <t>331653</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>408808</t>
+          <t>405898</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>313341</t>
+          <t>314716</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>385021</t>
+          <t>387911</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>468254</t>
+          <t>474982</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>558552</t>
+          <t>563131</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>808356</t>
+          <t>813679</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>923926</t>
+          <t>924094</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2718164</t>
+          <t>2717119</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2813069</t>
+          <t>2811798</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2377206</t>
+          <t>2380608</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2498294</t>
+          <t>2495209</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5129733</t>
+          <t>5135148</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5279957</t>
+          <t>5282679</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>75,86%</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según dificultad en su trabajo habitual las últimas 4 semanas por el dolor en 2016</t>
+          <t>Población según dificultad en su trabajo habitual las últimas 4 semanas por el dolor en 2016 (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21901</t>
+          <t>20325</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17615</t>
+          <t>17892</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39175</t>
+          <t>38718</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27769</t>
+          <t>28244</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51859</t>
+          <t>53266</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11084</t>
+          <t>11030</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27286</t>
+          <t>29035</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36469</t>
+          <t>36841</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65464</t>
+          <t>64889</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53667</t>
+          <t>51099</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>88384</t>
+          <t>86199</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14541</t>
+          <t>14108</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34328</t>
+          <t>34372</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23826</t>
+          <t>24235</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47529</t>
+          <t>48006</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>44355</t>
+          <t>44681</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>76270</t>
+          <t>75670</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69019</t>
+          <t>68663</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>102502</t>
+          <t>102619</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>87273</t>
+          <t>86648</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>124640</t>
+          <t>124772</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>164702</t>
+          <t>164675</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>216358</t>
+          <t>213500</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>15,99%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>511797</t>
+          <t>511029</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>550953</t>
+          <t>552905</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>424146</t>
+          <t>424766</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>476576</t>
+          <t>475360</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>947196</t>
+          <t>945989</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1011024</t>
+          <t>1012455</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>75,83%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5615</t>
+          <t>5358</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18374</t>
+          <t>18856</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13041</t>
+          <t>12876</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32526</t>
+          <t>32824</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21747</t>
+          <t>20970</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46194</t>
+          <t>45028</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17414</t>
+          <t>16805</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39013</t>
+          <t>37251</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47449</t>
+          <t>47687</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>82310</t>
+          <t>79260</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>70158</t>
+          <t>70344</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>111520</t>
+          <t>110621</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>33024</t>
+          <t>32510</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>60239</t>
+          <t>58892</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>60889</t>
+          <t>61072</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>96833</t>
+          <t>98337</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>100891</t>
+          <t>101124</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>145877</t>
+          <t>146872</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>87181</t>
+          <t>91639</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>128776</t>
+          <t>128432</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>131345</t>
+          <t>130908</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>179152</t>
+          <t>177703</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>233522</t>
+          <t>232040</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>292164</t>
+          <t>293898</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,3%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>800743</t>
+          <t>800109</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>852428</t>
+          <t>847782</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>693115</t>
+          <t>692527</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>755922</t>
+          <t>754821</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1510657</t>
+          <t>1511894</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1594074</t>
+          <t>1594203</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,55%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4878</t>
+          <t>4842</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19465</t>
+          <t>18506</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18112</t>
+          <t>18686</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41774</t>
+          <t>41399</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25286</t>
+          <t>26172</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50580</t>
+          <t>54673</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10495</t>
+          <t>10883</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27261</t>
+          <t>28120</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30946</t>
+          <t>29950</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>57181</t>
+          <t>57178</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>45582</t>
+          <t>45495</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>75781</t>
+          <t>77183</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21677</t>
+          <t>22516</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>44492</t>
+          <t>46496</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>23953</t>
+          <t>25354</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>47520</t>
+          <t>48924</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>50259</t>
+          <t>51573</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>84187</t>
+          <t>84979</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>55991</t>
+          <t>54006</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>88640</t>
+          <t>86642</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>83912</t>
+          <t>84243</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>121902</t>
+          <t>124243</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>147911</t>
+          <t>148714</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>198697</t>
+          <t>200958</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>600538</t>
+          <t>597072</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>642145</t>
+          <t>642089</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>543803</t>
+          <t>544185</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>594750</t>
+          <t>595596</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1158490</t>
+          <t>1158068</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1225858</t>
+          <t>1227103</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>80,14%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7347</t>
+          <t>7250</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22056</t>
+          <t>22311</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20972</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>45526</t>
+          <t>44244</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32856</t>
+          <t>32815</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>61119</t>
+          <t>60945</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10153,7 +10153,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>21310</t>
+          <t>21509</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>44987</t>
+          <t>44197</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>46453</t>
+          <t>45832</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>80279</t>
+          <t>80055</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>74055</t>
+          <t>74577</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>113980</t>
+          <t>114272</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>26574</t>
+          <t>26026</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>49687</t>
+          <t>49843</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>43424</t>
+          <t>43067</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>75168</t>
+          <t>77154</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>76599</t>
+          <t>76409</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>115711</t>
+          <t>117287</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>69476</t>
+          <t>69226</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>103570</t>
+          <t>106906</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>103999</t>
+          <t>106903</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>150516</t>
+          <t>148815</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>186924</t>
+          <t>186343</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>245053</t>
+          <t>245443</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,46%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>739045</t>
+          <t>736975</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>786839</t>
+          <t>786262</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>727515</t>
+          <t>730040</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>791260</t>
+          <t>789435</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1487196</t>
+          <t>1484129</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1561157</t>
+          <t>1563671</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>79,4%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>34693</t>
+          <t>34154</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>59620</t>
+          <t>59052</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>86209</t>
+          <t>88935</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>130762</t>
+          <t>131055</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>128766</t>
+          <t>127088</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>181168</t>
+          <t>180375</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>75695</t>
+          <t>76625</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>116635</t>
+          <t>115500</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>185100</t>
+          <t>182199</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>243815</t>
+          <t>243104</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>273671</t>
+          <t>274178</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>348121</t>
+          <t>345707</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>113739</t>
+          <t>113842</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>162705</t>
+          <t>159872</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>175209</t>
+          <t>177334</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>237161</t>
+          <t>236549</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>304905</t>
+          <t>303179</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>379244</t>
+          <t>380217</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>318578</t>
+          <t>314698</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>391000</t>
+          <t>387691</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>447170</t>
+          <t>444898</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>529121</t>
+          <t>530921</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>786135</t>
+          <t>782420</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>897863</t>
+          <t>894099</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2698780</t>
+          <t>2693967</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2785116</t>
+          <t>2786238</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2448372</t>
+          <t>2450668</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2558723</t>
+          <t>2562916</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5175146</t>
+          <t>5170707</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5323916</t>
+          <t>5315299</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,13%</t>
         </is>
       </c>
     </row>
@@ -11464,7 +11464,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según dificultad en su trabajo habitual las últimas 4 semanas por el dolor en 2023</t>
+          <t>Población según dificultad en su trabajo habitual las últimas 4 semanas por el dolor en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11659,12 +11659,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17928</t>
+          <t>18100</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36762</t>
+          <t>36157</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11674,12 +11674,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11694,12 +11694,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30810</t>
+          <t>30288</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45693</t>
+          <t>46318</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11709,12 +11709,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52096</t>
+          <t>52312</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>76162</t>
+          <t>77034</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11744,12 +11744,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -11772,12 +11772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32643</t>
+          <t>32600</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56589</t>
+          <t>57345</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48098</t>
+          <t>48559</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>69388</t>
+          <t>69986</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11822,12 +11822,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>84105</t>
+          <t>85276</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>117817</t>
+          <t>118259</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -11885,12 +11885,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43064</t>
+          <t>43026</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>69179</t>
+          <t>68635</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>67088</t>
+          <t>66498</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>91760</t>
+          <t>91552</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11935,12 +11935,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>114462</t>
+          <t>113733</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>150142</t>
+          <t>151700</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11970,12 +11970,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58040</t>
+          <t>58950</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>89104</t>
+          <t>87654</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>84954</t>
+          <t>84917</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>112438</t>
+          <t>111704</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12053,7 +12053,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>153059</t>
+          <t>150492</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>192272</t>
+          <t>189404</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,45%</t>
         </is>
       </c>
     </row>
@@ -12111,12 +12111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>416060</t>
+          <t>415931</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>461896</t>
+          <t>462078</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12126,12 +12126,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>384667</t>
+          <t>383221</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>423199</t>
+          <t>423994</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>811719</t>
+          <t>813130</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>875395</t>
+          <t>875352</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12196,7 +12196,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -12341,12 +12341,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9980</t>
+          <t>9453</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30854</t>
+          <t>30732</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12356,12 +12356,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35229</t>
+          <t>35341</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54894</t>
+          <t>55328</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12391,12 +12391,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43308</t>
+          <t>41268</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79053</t>
+          <t>79977</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21953</t>
+          <t>18199</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57394</t>
+          <t>56756</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12484,17 +12484,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>74767</t>
+          <t>74766</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62218</t>
+          <t>63304</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>89929</t>
+          <t>89990</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>75565</t>
+          <t>75892</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>138960</t>
+          <t>139399</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34672</t>
+          <t>30708</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>90157</t>
+          <t>90402</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>81777</t>
+          <t>82143</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>113626</t>
+          <t>113625</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,7 +12617,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>104133</t>
+          <t>105876</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>194410</t>
+          <t>191128</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -12680,12 +12680,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53328</t>
+          <t>46947</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>139127</t>
+          <t>140904</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12695,82 +12695,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>11,84%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>147633</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>132085</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>166915</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>15,43%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>13,81%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>17,45%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>384</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>251068</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>159409</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>292434</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
           <t>11,69%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>147633</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>130872</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>166123</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>15,43%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>13,68%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>17,37%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>251068</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>169861</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>293888</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>11,69%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,62%</t>
         </is>
       </c>
     </row>
@@ -12793,12 +12793,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>891944</t>
+          <t>889126</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1065214</t>
+          <t>1079327</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12808,12 +12808,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>570228</t>
+          <t>567247</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>620597</t>
+          <t>617617</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1460190</t>
+          <t>1467774</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1743583</t>
+          <t>1766201</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>82,26%</t>
         </is>
       </c>
     </row>
@@ -13023,12 +13023,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5338</t>
+          <t>5407</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19469</t>
+          <t>18912</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13038,12 +13038,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6251</t>
+          <t>6015</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21253</t>
+          <t>21585</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13073,12 +13073,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15212</t>
+          <t>14596</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36309</t>
+          <t>34403</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13108,12 +13108,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -13136,12 +13136,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24188</t>
+          <t>23651</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>47775</t>
+          <t>47533</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21341</t>
+          <t>20549</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>59324</t>
+          <t>57703</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>48745</t>
+          <t>48366</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>94711</t>
+          <t>93614</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -13249,12 +13249,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25281</t>
+          <t>26384</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>49005</t>
+          <t>51028</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>29552</t>
+          <t>27867</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>83214</t>
+          <t>82194</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>64895</t>
+          <t>64348</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>120304</t>
+          <t>120194</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -13362,12 +13362,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>68176</t>
+          <t>69680</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>107288</t>
+          <t>105937</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>125878</t>
+          <t>126193</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>581620</t>
+          <t>650760</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>209880</t>
+          <t>210326</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>801737</t>
+          <t>800970</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>48,92%</t>
         </is>
       </c>
     </row>
@@ -13475,12 +13475,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>511766</t>
+          <t>513195</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>557940</t>
+          <t>560312</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13490,12 +13490,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13510,12 +13510,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>275129</t>
+          <t>221197</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>662401</t>
+          <t>665396</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13545,12 +13545,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>696160</t>
+          <t>715879</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1208119</t>
+          <t>1207012</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>73,71%</t>
         </is>
       </c>
     </row>
@@ -13705,12 +13705,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13821</t>
+          <t>14681</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32770</t>
+          <t>33106</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13720,82 +13720,82 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>3,57%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>49592</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>37993</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>62800</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>4,54%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>3,48%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>5,75%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>71568</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>57723</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>86970</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
           <t>3,54%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>49592</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>38383</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>62407</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>4,54%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>3,51%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>5,71%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>71568</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>58122</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>87204</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>51926</t>
+          <t>51187</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>79618</t>
+          <t>78660</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>82744</t>
+          <t>81084</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>128472</t>
+          <t>126105</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>144431</t>
+          <t>144017</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>194537</t>
+          <t>193755</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,59%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>39082</t>
+          <t>39120</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>66745</t>
+          <t>67038</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>66267</t>
+          <t>68542</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>102503</t>
+          <t>104193</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>117713</t>
+          <t>117076</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>162492</t>
+          <t>159302</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -14044,12 +14044,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>108157</t>
+          <t>107616</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>155513</t>
+          <t>153812</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>136972</t>
+          <t>137881</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>196366</t>
+          <t>196228</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>263948</t>
+          <t>262121</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>333559</t>
+          <t>330618</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,37%</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>632441</t>
+          <t>630328</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>689006</t>
+          <t>687284</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14192,12 +14192,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>639956</t>
+          <t>639338</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>761630</t>
+          <t>762518</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14207,12 +14207,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1293605</t>
+          <t>1301183</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1421215</t>
+          <t>1419714</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>70,29%</t>
         </is>
       </c>
     </row>
@@ -14387,12 +14387,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>58773</t>
+          <t>59198</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>98496</t>
+          <t>97564</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14402,12 +14402,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>119011</t>
+          <t>117607</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>166152</t>
+          <t>166442</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>192103</t>
+          <t>187351</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>256143</t>
+          <t>252332</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>141191</t>
+          <t>140481</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>213025</t>
+          <t>208726</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>225433</t>
+          <t>224785</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>312830</t>
+          <t>313763</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>405029</t>
+          <t>402104</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>505348</t>
+          <t>508428</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>164860</t>
+          <t>164714</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>242425</t>
+          <t>239949</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>248878</t>
+          <t>261717</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>353828</t>
+          <t>355224</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>458403</t>
+          <t>457065</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>580304</t>
+          <t>581400</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>304773</t>
+          <t>304971</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>439986</t>
+          <t>441924</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14746,7 +14746,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>540087</t>
+          <t>541180</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1260754</t>
+          <t>1294297</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>898891</t>
+          <t>911788</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1753706</t>
+          <t>1732883</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,36%</t>
         </is>
       </c>
     </row>
@@ -14834,17 +14834,17 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2596949</t>
+          <t>2596950</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2507068</t>
+          <t>2510202</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2780205</t>
+          <t>2785837</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1800960</t>
+          <t>1767201</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2348753</t>
+          <t>2343286</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14889,12 +14889,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>64,05%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4258600</t>
+          <t>4340934</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5005895</t>
+          <t>5005468</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14924,12 +14924,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>70,35%</t>
         </is>
       </c>
     </row>
@@ -14947,17 +14947,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3456754</t>
+          <t>3456755</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3456754</t>
+          <t>3456755</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3456754</t>
+          <t>3456755</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">

--- a/data/trans_orig/P11-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P11-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>2511</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13068</t>
+          <t>12930</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,47 +748,47 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>5192</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1948</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>11751</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
           <t>0,28%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5192</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1977</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>12367</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>6253</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21054</t>
+          <t>21348</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6905</t>
+          <t>6737</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20334</t>
+          <t>21297</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9442</t>
+          <t>8775</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24280</t>
+          <t>25422</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19475</t>
+          <t>19692</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39986</t>
+          <t>40099</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29283</t>
+          <t>28212</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53947</t>
+          <t>51303</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>44536</t>
+          <t>44539</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>71231</t>
+          <t>73097</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>76958</t>
+          <t>80499</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116072</t>
+          <t>116639</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>78702</t>
+          <t>78195</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>113964</t>
+          <t>113272</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>108206</t>
+          <t>109069</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>149657</t>
+          <t>148210</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>196473</t>
+          <t>196337</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>247656</t>
+          <t>249333</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,04%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>518284</t>
+          <t>520684</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>560251</t>
+          <t>562158</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>457792</t>
+          <t>458582</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>504372</t>
+          <t>505689</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>992417</t>
+          <t>989050</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1054454</t>
+          <t>1054796</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,3%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4776</t>
+          <t>4213</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17529</t>
+          <t>16481</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6188</t>
+          <t>5366</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21962</t>
+          <t>21687</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13749</t>
+          <t>12782</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33765</t>
+          <t>33033</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20454</t>
+          <t>20203</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42547</t>
+          <t>44030</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19837</t>
+          <t>18938</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41307</t>
+          <t>39103</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>44569</t>
+          <t>44525</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>74877</t>
+          <t>75202</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32580</t>
+          <t>33313</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>59290</t>
+          <t>58695</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>50783</t>
+          <t>49802</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>85676</t>
+          <t>81494</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>90883</t>
+          <t>89351</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>134382</t>
+          <t>131199</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52438</t>
+          <t>52154</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83849</t>
+          <t>82430</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>129978</t>
+          <t>129367</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>175620</t>
+          <t>174783</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>191595</t>
+          <t>193225</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>248156</t>
+          <t>249181</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,91%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>787573</t>
+          <t>789391</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>832462</t>
+          <t>833829</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>679227</t>
+          <t>683525</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>736834</t>
+          <t>741664</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1487392</t>
+          <t>1484485</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1557767</t>
+          <t>1556708</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,65%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3803</t>
+          <t>3444</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16727</t>
+          <t>14937</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7767</t>
+          <t>8473</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22758</t>
+          <t>22309</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14759</t>
+          <t>13806</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34155</t>
+          <t>32376</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9353</t>
+          <t>9216</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28269</t>
+          <t>26640</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>32319</t>
+          <t>33618</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>58580</t>
+          <t>59635</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>46203</t>
+          <t>47539</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>78545</t>
+          <t>80251</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18638</t>
+          <t>18456</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>38729</t>
+          <t>38414</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>42999</t>
+          <t>42912</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>70156</t>
+          <t>71539</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>65034</t>
+          <t>67126</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>100956</t>
+          <t>100670</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>63551</t>
+          <t>62709</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>99591</t>
+          <t>98522</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>105427</t>
+          <t>106947</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>144970</t>
+          <t>145292</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>180568</t>
+          <t>181946</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>233548</t>
+          <t>236381</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,35%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>522729</t>
+          <t>524030</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>567470</t>
+          <t>567439</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>417810</t>
+          <t>419227</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>468274</t>
+          <t>471633</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>958422</t>
+          <t>957013</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1024679</t>
+          <t>1024077</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,17%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2591</t>
+          <t>2585</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12378</t>
+          <t>12271</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13999</t>
+          <t>13404</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32553</t>
+          <t>32580</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18798</t>
+          <t>18507</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>40411</t>
+          <t>38555</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17077</t>
+          <t>16924</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>38178</t>
+          <t>35647</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>23714</t>
+          <t>24403</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>47543</t>
+          <t>47362</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>45803</t>
+          <t>45305</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>75402</t>
+          <t>73118</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20504</t>
+          <t>20958</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>41924</t>
+          <t>42067</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>62290</t>
+          <t>62764</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>97584</t>
+          <t>96301</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>89935</t>
+          <t>89942</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>132452</t>
+          <t>130681</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>83343</t>
+          <t>82470</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>118808</t>
+          <t>119836</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>126184</t>
+          <t>127640</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>173002</t>
+          <t>174471</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>223245</t>
+          <t>218531</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>280865</t>
+          <t>277430</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>758342</t>
+          <t>758487</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>802231</t>
+          <t>803955</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>723424</t>
+          <t>726769</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>783592</t>
+          <t>783398</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1497289</t>
+          <t>1501476</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1571085</t>
+          <t>1573844</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,45%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>21023</t>
+          <t>20086</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>42271</t>
+          <t>42345</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>38818</t>
+          <t>40053</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>69240</t>
+          <t>70830</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>66961</t>
+          <t>67439</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>102020</t>
+          <t>103400</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>69919</t>
+          <t>70225</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>105626</t>
+          <t>106696</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>102685</t>
+          <t>101151</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>145501</t>
+          <t>145393</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>181541</t>
+          <t>179600</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>236082</t>
+          <t>234712</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>118111</t>
+          <t>120007</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>163093</t>
+          <t>165108</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>225766</t>
+          <t>228142</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>287453</t>
+          <t>289526</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>359883</t>
+          <t>358742</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>437766</t>
+          <t>437965</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,7 +3772,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>305354</t>
+          <t>308123</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>374715</t>
+          <t>376279</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>509992</t>
+          <t>509796</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>600860</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>835059</t>
+          <t>840600</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>950142</t>
+          <t>953077</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,32%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2633467</t>
+          <t>2636569</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2722206</t>
+          <t>2723299</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2336818</t>
+          <t>2334513</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2445226</t>
+          <t>2440383</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5006041</t>
+          <t>5006945</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5144842</t>
+          <t>5147285</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,34%</t>
         </is>
       </c>
     </row>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7946</t>
+          <t>7643</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24378</t>
+          <t>23047</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17363</t>
+          <t>17027</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37374</t>
+          <t>36920</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28902</t>
+          <t>28799</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54103</t>
+          <t>55219</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17799</t>
+          <t>17831</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39092</t>
+          <t>39144</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40736</t>
+          <t>40018</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>69593</t>
+          <t>70340</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>65125</t>
+          <t>62868</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>98416</t>
+          <t>99137</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21517</t>
+          <t>21663</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43329</t>
+          <t>44937</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>38461</t>
+          <t>38168</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>65578</t>
+          <t>67021</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>65626</t>
+          <t>65946</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>102912</t>
+          <t>103801</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45322</t>
+          <t>47003</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75971</t>
+          <t>75825</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>87243</t>
+          <t>87337</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>127653</t>
+          <t>127621</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>144009</t>
+          <t>141203</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>194766</t>
+          <t>188456</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>543468</t>
+          <t>545584</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>585680</t>
+          <t>586648</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>429748</t>
+          <t>431782</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>485158</t>
+          <t>484805</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>989387</t>
+          <t>992344</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1056008</t>
+          <t>1058151</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>75,96%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9907</t>
+          <t>9587</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26938</t>
+          <t>26380</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24047</t>
+          <t>22910</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47847</t>
+          <t>48070</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38538</t>
+          <t>37776</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67154</t>
+          <t>67265</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23623</t>
+          <t>23650</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48774</t>
+          <t>47685</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54667</t>
+          <t>54586</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>90097</t>
+          <t>89181</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>84873</t>
+          <t>86189</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>124460</t>
+          <t>127787</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25322</t>
+          <t>26193</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48758</t>
+          <t>49966</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>49843</t>
+          <t>50376</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>82020</t>
+          <t>84142</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>83573</t>
+          <t>82865</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>123433</t>
+          <t>122606</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>103516</t>
+          <t>102158</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>147023</t>
+          <t>146774</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>132426</t>
+          <t>132304</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>178769</t>
+          <t>178109</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>247600</t>
+          <t>245167</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>311163</t>
+          <t>310814</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,21%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>776945</t>
+          <t>775980</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>830707</t>
+          <t>831321</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>674993</t>
+          <t>674606</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>736529</t>
+          <t>737280</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1467482</t>
+          <t>1466134</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1546760</t>
+          <t>1551434</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,91%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5417</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21207</t>
+          <t>21527</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15695</t>
+          <t>16070</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37790</t>
+          <t>37694</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26342</t>
+          <t>25673</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50861</t>
+          <t>50251</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11292</t>
+          <t>10811</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31318</t>
+          <t>32241</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34003</t>
+          <t>34485</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>62422</t>
+          <t>62171</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>50482</t>
+          <t>51327</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>87661</t>
+          <t>87341</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10212</t>
+          <t>9566</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30332</t>
+          <t>29679</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32665</t>
+          <t>32570</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>59370</t>
+          <t>60270</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>47999</t>
+          <t>47455</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>81347</t>
+          <t>78831</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>39251</t>
+          <t>36825</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>67875</t>
+          <t>65938</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>84939</t>
+          <t>85099</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>123223</t>
+          <t>123602</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>130359</t>
+          <t>131947</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>179218</t>
+          <t>180906</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>631831</t>
+          <t>632890</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>671619</t>
+          <t>672929</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>530502</t>
+          <t>531242</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>582124</t>
+          <t>581230</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1176403</t>
+          <t>1179255</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1243414</t>
+          <t>1245364</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,31%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5807</t>
+          <t>5831</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19799</t>
+          <t>20382</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18906</t>
+          <t>18180</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39364</t>
+          <t>39670</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27268</t>
+          <t>28181</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>52915</t>
+          <t>52461</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>28411</t>
+          <t>28886</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>55628</t>
+          <t>54993</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>51734</t>
+          <t>51537</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>85183</t>
+          <t>84019</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>88317</t>
+          <t>87141</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>130496</t>
+          <t>130197</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>24245</t>
+          <t>25036</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>48887</t>
+          <t>47281</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>68830</t>
+          <t>67533</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>102446</t>
+          <t>104410</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>98507</t>
+          <t>98958</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>141102</t>
+          <t>141143</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,7 +6732,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>95125</t>
+          <t>96180</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>137321</t>
+          <t>138811</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>130262</t>
+          <t>130685</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>177641</t>
+          <t>179080</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>236979</t>
+          <t>238437</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>301638</t>
+          <t>299385</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,0%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>716927</t>
+          <t>712570</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>768250</t>
+          <t>765594</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>687864</t>
+          <t>686682</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>746734</t>
+          <t>747907</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1418409</t>
+          <t>1423005</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1501408</t>
+          <t>1500854</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,2%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>39638</t>
+          <t>39199</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>70260</t>
+          <t>68889</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>94622</t>
+          <t>93848</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>139186</t>
+          <t>138125</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>142552</t>
+          <t>142384</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>194847</t>
+          <t>194991</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>97736</t>
+          <t>98000</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>143622</t>
+          <t>144976</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>206877</t>
+          <t>205395</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>267523</t>
+          <t>270020</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>320164</t>
+          <t>322396</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>397484</t>
+          <t>395398</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>100001</t>
+          <t>98980</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>142744</t>
+          <t>144136</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>214295</t>
+          <t>217182</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>277515</t>
+          <t>280365</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>331653</t>
+          <t>328256</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>405898</t>
+          <t>405861</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>314716</t>
+          <t>314659</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>387911</t>
+          <t>388639</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>474982</t>
+          <t>473567</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>563131</t>
+          <t>557455</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>813679</t>
+          <t>812822</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>924094</t>
+          <t>924088</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2717119</t>
+          <t>2716903</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2811798</t>
+          <t>2812474</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2380608</t>
+          <t>2388872</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2495209</t>
+          <t>2499488</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5135148</t>
+          <t>5129558</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5282679</t>
+          <t>5277617</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,78%</t>
         </is>
       </c>
     </row>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6310</t>
+          <t>6277</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20325</t>
+          <t>19559</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17892</t>
+          <t>18027</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38718</t>
+          <t>39205</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28244</t>
+          <t>27316</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53266</t>
+          <t>51659</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11030</t>
+          <t>11463</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29035</t>
+          <t>28742</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36841</t>
+          <t>37068</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64889</t>
+          <t>65263</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51099</t>
+          <t>51815</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>86199</t>
+          <t>84516</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14108</t>
+          <t>15242</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34372</t>
+          <t>37241</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24235</t>
+          <t>24232</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>48006</t>
+          <t>49018</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>44681</t>
+          <t>44170</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>75670</t>
+          <t>75564</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68663</t>
+          <t>68160</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>102619</t>
+          <t>104896</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>86648</t>
+          <t>86081</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>124772</t>
+          <t>124257</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>164675</t>
+          <t>165552</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>213500</t>
+          <t>217026</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,26%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>511029</t>
+          <t>510326</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>552905</t>
+          <t>552614</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>424766</t>
+          <t>425137</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>475360</t>
+          <t>473061</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>945989</t>
+          <t>947832</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1012455</t>
+          <t>1013837</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>75,94%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5358</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18856</t>
+          <t>20131</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12876</t>
+          <t>12624</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32824</t>
+          <t>32302</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20970</t>
+          <t>22381</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45028</t>
+          <t>45854</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16805</t>
+          <t>17573</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37251</t>
+          <t>40052</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47687</t>
+          <t>45985</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>79260</t>
+          <t>79885</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>70344</t>
+          <t>70340</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>110621</t>
+          <t>110059</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8902,7 +8902,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32510</t>
+          <t>33621</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>58892</t>
+          <t>58095</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>61072</t>
+          <t>59369</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>98337</t>
+          <t>96711</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>101124</t>
+          <t>102279</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>146872</t>
+          <t>148406</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>91639</t>
+          <t>89643</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>128432</t>
+          <t>130216</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>130908</t>
+          <t>130632</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>177703</t>
+          <t>178282</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>232040</t>
+          <t>233239</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>293898</t>
+          <t>295419</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,37%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>800109</t>
+          <t>802771</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>847782</t>
+          <t>850675</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>692527</t>
+          <t>692299</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>754821</t>
+          <t>753870</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>66,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>72,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1511894</t>
+          <t>1508463</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1594203</t>
+          <t>1587823</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,24%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4842</t>
+          <t>4887</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18506</t>
+          <t>18448</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18686</t>
+          <t>18562</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41399</t>
+          <t>41340</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26172</t>
+          <t>26455</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54673</t>
+          <t>53515</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10883</t>
+          <t>10718</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28120</t>
+          <t>27508</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29950</t>
+          <t>28877</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>57178</t>
+          <t>55574</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>45495</t>
+          <t>44807</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>77183</t>
+          <t>75355</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22516</t>
+          <t>21738</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>46496</t>
+          <t>45840</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>25354</t>
+          <t>24598</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>48924</t>
+          <t>47053</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>51573</t>
+          <t>50820</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>84979</t>
+          <t>85213</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>54006</t>
+          <t>54426</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>86642</t>
+          <t>87169</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>84243</t>
+          <t>87073</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>124243</t>
+          <t>126125</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>148714</t>
+          <t>149604</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>200958</t>
+          <t>200265</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>597072</t>
+          <t>598401</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>642089</t>
+          <t>642491</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>544185</t>
+          <t>543365</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>595596</t>
+          <t>594577</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1158068</t>
+          <t>1161262</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1227103</t>
+          <t>1227590</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>80,17%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7250</t>
+          <t>7188</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22311</t>
+          <t>22750</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>21074</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44244</t>
+          <t>44836</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32815</t>
+          <t>32207</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>60945</t>
+          <t>60019</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>21509</t>
+          <t>22493</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>44197</t>
+          <t>46932</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>45832</t>
+          <t>46619</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>80055</t>
+          <t>80018</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>74577</t>
+          <t>74383</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>114272</t>
+          <t>114688</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>26026</t>
+          <t>27021</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>49843</t>
+          <t>49908</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>43067</t>
+          <t>43500</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>77154</t>
+          <t>75758</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>76409</t>
+          <t>77768</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>117287</t>
+          <t>116616</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>69226</t>
+          <t>70487</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>106906</t>
+          <t>106421</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>106903</t>
+          <t>106743</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>148815</t>
+          <t>152061</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>186343</t>
+          <t>185727</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>245443</t>
+          <t>242192</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,3%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>736975</t>
+          <t>737594</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>786262</t>
+          <t>785650</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>730040</t>
+          <t>731590</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>789435</t>
+          <t>788843</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1484129</t>
+          <t>1484234</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1563671</t>
+          <t>1563319</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,38%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>34154</t>
+          <t>32966</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>59052</t>
+          <t>59615</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>88935</t>
+          <t>86688</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>131055</t>
+          <t>129041</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>127088</t>
+          <t>128829</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>180375</t>
+          <t>180172</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>76625</t>
+          <t>76619</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>115500</t>
+          <t>114631</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>182199</t>
+          <t>185447</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>243104</t>
+          <t>245472</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>274178</t>
+          <t>271792</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>345707</t>
+          <t>343541</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>113842</t>
+          <t>114657</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>159872</t>
+          <t>158899</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>177334</t>
+          <t>177484</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>236549</t>
+          <t>236569</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>303179</t>
+          <t>304896</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>380217</t>
+          <t>381520</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>314698</t>
+          <t>316217</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>387691</t>
+          <t>385580</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>444898</t>
+          <t>441517</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>530921</t>
+          <t>528302</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>782420</t>
+          <t>784923</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>894099</t>
+          <t>897226</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,02%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2693967</t>
+          <t>2695858</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2786238</t>
+          <t>2783724</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2450668</t>
+          <t>2456890</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2562916</t>
+          <t>2564499</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5170707</t>
+          <t>5180611</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5315299</t>
+          <t>5321559</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>77,22%</t>
         </is>
       </c>
     </row>
@@ -11654,32 +11654,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>25513</t>
+          <t>26889</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18100</t>
+          <t>18212</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36157</t>
+          <t>38272</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11689,32 +11689,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>37669</t>
+          <t>39620</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30288</t>
+          <t>31571</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46318</t>
+          <t>47548</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11724,32 +11724,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>63182</t>
+          <t>66508</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52312</t>
+          <t>55008</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>77034</t>
+          <t>81553</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -11767,32 +11767,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>43409</t>
+          <t>44599</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32600</t>
+          <t>34457</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57345</t>
+          <t>60054</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11802,32 +11802,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>57869</t>
+          <t>61992</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48559</t>
+          <t>51609</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>69986</t>
+          <t>73786</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11837,32 +11837,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>101278</t>
+          <t>106591</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>85276</t>
+          <t>90416</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>118259</t>
+          <t>123101</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -11880,32 +11880,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>54739</t>
+          <t>58099</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43026</t>
+          <t>46161</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>68635</t>
+          <t>71878</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11915,32 +11915,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>76981</t>
+          <t>80709</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>66498</t>
+          <t>67669</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>91552</t>
+          <t>94234</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11950,32 +11950,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>131720</t>
+          <t>138808</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>113733</t>
+          <t>121285</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>151700</t>
+          <t>159350</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -11993,32 +11993,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>72243</t>
+          <t>81669</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58950</t>
+          <t>65625</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>87654</t>
+          <t>98713</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12028,32 +12028,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>98701</t>
+          <t>106196</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>84917</t>
+          <t>91558</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>111704</t>
+          <t>120769</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12063,32 +12063,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>170945</t>
+          <t>187865</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>150492</t>
+          <t>167386</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>189404</t>
+          <t>212591</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,94%</t>
         </is>
       </c>
     </row>
@@ -12106,32 +12106,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>438806</t>
+          <t>478449</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>415931</t>
+          <t>454355</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>462078</t>
+          <t>501315</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12141,32 +12141,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>404531</t>
+          <t>444597</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>383221</t>
+          <t>424029</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>423994</t>
+          <t>466534</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12176,32 +12176,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>843338</t>
+          <t>923047</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>813130</t>
+          <t>885651</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>875352</t>
+          <t>953313</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>67,0%</t>
         </is>
       </c>
     </row>
@@ -12219,17 +12219,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>634710</t>
+          <t>689705</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>634710</t>
+          <t>689705</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>634710</t>
+          <t>689705</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12254,17 +12254,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -12289,17 +12289,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1310463</t>
+          <t>1422819</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1310463</t>
+          <t>1422819</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1310463</t>
+          <t>1422819</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -12336,32 +12336,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>19894</t>
+          <t>22451</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9453</t>
+          <t>14494</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30732</t>
+          <t>32907</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12371,32 +12371,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>44165</t>
+          <t>48805</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35341</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55328</t>
+          <t>60374</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12406,32 +12406,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>64059</t>
+          <t>71257</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41268</t>
+          <t>57624</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79977</t>
+          <t>86085</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -12449,32 +12449,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>40604</t>
+          <t>44846</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18199</t>
+          <t>32259</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56756</t>
+          <t>58866</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12484,32 +12484,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>74766</t>
+          <t>86451</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63304</t>
+          <t>72651</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>89990</t>
+          <t>104582</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12519,32 +12519,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>115371</t>
+          <t>131297</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>75892</t>
+          <t>113314</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>139399</t>
+          <t>154740</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -12562,32 +12562,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>65470</t>
+          <t>70175</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30708</t>
+          <t>54609</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>90402</t>
+          <t>86945</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12597,32 +12597,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>96434</t>
+          <t>104057</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>82143</t>
+          <t>89117</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>113625</t>
+          <t>121635</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12632,32 +12632,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>161904</t>
+          <t>174231</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>105876</t>
+          <t>153702</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>191128</t>
+          <t>197758</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -12675,32 +12675,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>103434</t>
+          <t>113010</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46947</t>
+          <t>92841</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>140904</t>
+          <t>135548</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12710,32 +12710,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>147633</t>
+          <t>159646</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>132085</t>
+          <t>140583</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>166915</t>
+          <t>177823</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12745,32 +12745,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>251068</t>
+          <t>272656</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>159409</t>
+          <t>244936</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>292434</t>
+          <t>301297</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>14,24%</t>
         </is>
       </c>
     </row>
@@ -12788,32 +12788,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>961130</t>
+          <t>795817</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>889126</t>
+          <t>767966</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1079327</t>
+          <t>826015</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12823,32 +12823,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>593631</t>
+          <t>670242</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>567247</t>
+          <t>643549</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>617617</t>
+          <t>698314</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12858,32 +12858,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1554761</t>
+          <t>1466059</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1467774</t>
+          <t>1425178</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1766201</t>
+          <t>1508155</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>71,29%</t>
         </is>
       </c>
     </row>
@@ -12901,17 +12901,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1190533</t>
+          <t>1046299</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1190533</t>
+          <t>1046299</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1190533</t>
+          <t>1046299</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12936,17 +12936,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>956630</t>
+          <t>1069200</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>956630</t>
+          <t>1069200</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>956630</t>
+          <t>1069200</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12971,17 +12971,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2147163</t>
+          <t>2115500</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2147163</t>
+          <t>2115500</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2147163</t>
+          <t>2115500</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -13018,32 +13018,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>11084</t>
+          <t>11780</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5407</t>
+          <t>6237</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18912</t>
+          <t>21352</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13053,32 +13053,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>13360</t>
+          <t>15634</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6015</t>
+          <t>10054</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21585</t>
+          <t>22993</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13088,32 +13088,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>24444</t>
+          <t>27414</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14596</t>
+          <t>19103</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34403</t>
+          <t>38215</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -13131,32 +13131,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>34131</t>
+          <t>38638</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23651</t>
+          <t>27629</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>47533</t>
+          <t>53301</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13166,32 +13166,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>41393</t>
+          <t>47876</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20549</t>
+          <t>38414</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>57703</t>
+          <t>60700</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13201,32 +13201,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>75523</t>
+          <t>86515</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>48366</t>
+          <t>70802</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>93614</t>
+          <t>104816</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -13244,27 +13244,27 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>37094</t>
+          <t>43779</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26384</t>
+          <t>31495</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>51028</t>
+          <t>58153</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -13279,32 +13279,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>59567</t>
+          <t>68071</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>27867</t>
+          <t>55479</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>82194</t>
+          <t>83168</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13314,32 +13314,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>96662</t>
+          <t>111850</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>64348</t>
+          <t>94378</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>120194</t>
+          <t>133187</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -13357,102 +13357,102 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>86470</t>
+          <t>98669</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>69680</t>
+          <t>78495</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>105937</t>
+          <t>120852</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
+          <t>15,05%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>117501</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>102296</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>136070</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>14,48%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>12,6%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>16,77%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>216170</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>190040</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>242644</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>13,39%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>11,77%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
           <t>15,03%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>308274</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>126193</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>650760</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>33,05%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>13,53%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>69,76%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>394744</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>210326</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>800970</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>24,11%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>12,84%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>48,92%</t>
         </is>
       </c>
     </row>
@@ -13470,32 +13470,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>535901</t>
+          <t>610206</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>513195</t>
+          <t>581536</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>560312</t>
+          <t>634484</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13505,32 +13505,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>510197</t>
+          <t>562520</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>221197</t>
+          <t>538953</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>665396</t>
+          <t>585367</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13540,32 +13540,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1046099</t>
+          <t>1172726</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>715879</t>
+          <t>1137803</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1207012</t>
+          <t>1207154</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>74,76%</t>
         </is>
       </c>
     </row>
@@ -13583,17 +13583,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -13618,17 +13618,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>932791</t>
+          <t>811602</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>932791</t>
+          <t>811602</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>932791</t>
+          <t>811602</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -13653,17 +13653,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1637472</t>
+          <t>1614675</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1637472</t>
+          <t>1614675</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1637472</t>
+          <t>1614675</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13700,32 +13700,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>21976</t>
+          <t>22723</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14681</t>
+          <t>15047</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33106</t>
+          <t>32940</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13735,32 +13735,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>49592</t>
+          <t>57832</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>37993</t>
+          <t>46376</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62800</t>
+          <t>71300</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13770,32 +13770,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>71568</t>
+          <t>80555</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>57723</t>
+          <t>66260</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>86970</t>
+          <t>95847</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -13813,32 +13813,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>64069</t>
+          <t>67292</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>51187</t>
+          <t>53854</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>78660</t>
+          <t>82910</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13848,32 +13848,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>103977</t>
+          <t>107340</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>81084</t>
+          <t>92126</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>126105</t>
+          <t>124210</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13883,32 +13883,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>168046</t>
+          <t>174632</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>144017</t>
+          <t>153798</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>193755</t>
+          <t>197792</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -13926,32 +13926,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>52339</t>
+          <t>54406</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>39120</t>
+          <t>41470</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>67038</t>
+          <t>69366</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13961,32 +13961,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>86550</t>
+          <t>94924</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>68542</t>
+          <t>81864</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>104193</t>
+          <t>112033</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13996,32 +13996,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>138889</t>
+          <t>149330</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>117076</t>
+          <t>128622</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>159302</t>
+          <t>172581</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -14039,32 +14039,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>127335</t>
+          <t>134286</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>107616</t>
+          <t>114668</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>153812</t>
+          <t>157842</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14074,32 +14074,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>173800</t>
+          <t>188441</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>137881</t>
+          <t>169102</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>196228</t>
+          <t>210756</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14109,32 +14109,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>301135</t>
+          <t>322727</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>262121</t>
+          <t>292322</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>330618</t>
+          <t>352643</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,74%</t>
         </is>
       </c>
     </row>
@@ -14152,32 +14152,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>661112</t>
+          <t>711355</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>630328</t>
+          <t>681735</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>687284</t>
+          <t>738769</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14187,32 +14187,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>679167</t>
+          <t>668341</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>639338</t>
+          <t>637185</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>762518</t>
+          <t>695804</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14222,32 +14222,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1340279</t>
+          <t>1379696</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1301183</t>
+          <t>1339034</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1419714</t>
+          <t>1423280</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>67,55%</t>
         </is>
       </c>
     </row>
@@ -14265,17 +14265,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -14300,17 +14300,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1093085</t>
+          <t>1116878</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1093085</t>
+          <t>1116878</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1093085</t>
+          <t>1116878</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -14335,17 +14335,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2019916</t>
+          <t>2106940</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2019916</t>
+          <t>2106940</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2019916</t>
+          <t>2106940</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -14382,32 +14382,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>78467</t>
+          <t>83844</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>59198</t>
+          <t>68621</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>97564</t>
+          <t>102325</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14417,32 +14417,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>144786</t>
+          <t>161891</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>117607</t>
+          <t>143532</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>166442</t>
+          <t>183766</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14452,32 +14452,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>223253</t>
+          <t>245734</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>187351</t>
+          <t>220700</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>252332</t>
+          <t>270579</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -14495,32 +14495,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>182213</t>
+          <t>195376</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>140481</t>
+          <t>170255</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>208726</t>
+          <t>223287</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14530,32 +14530,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>278005</t>
+          <t>303659</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>224785</t>
+          <t>276714</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>313763</t>
+          <t>334003</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14565,32 +14565,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>460218</t>
+          <t>499035</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>402104</t>
+          <t>460204</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>508428</t>
+          <t>541963</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -14608,32 +14608,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>209643</t>
+          <t>226458</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>164714</t>
+          <t>198677</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>239949</t>
+          <t>254605</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14643,32 +14643,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>319532</t>
+          <t>347760</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>261717</t>
+          <t>320643</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>355224</t>
+          <t>378642</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14678,32 +14678,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>529175</t>
+          <t>574218</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>457065</t>
+          <t>535616</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>581400</t>
+          <t>615467</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -14721,32 +14721,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>389482</t>
+          <t>427634</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>304971</t>
+          <t>390690</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>441924</t>
+          <t>471283</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14756,32 +14756,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>728409</t>
+          <t>571784</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>541180</t>
+          <t>537434</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1294297</t>
+          <t>611811</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14791,32 +14791,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1117891</t>
+          <t>999419</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>911788</t>
+          <t>948951</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1732883</t>
+          <t>1059039</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>14,59%</t>
         </is>
       </c>
     </row>
@@ -14834,32 +14834,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2596950</t>
+          <t>2595828</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2510202</t>
+          <t>2543196</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2785837</t>
+          <t>2654007</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14869,32 +14869,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2187527</t>
+          <t>2345700</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1767201</t>
+          <t>2295414</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2343286</t>
+          <t>2399452</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>62,87%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14904,32 +14904,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>4784476</t>
+          <t>4941528</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4340934</t>
+          <t>4858004</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5005468</t>
+          <t>5015500</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>69,08%</t>
         </is>
       </c>
     </row>
@@ -14947,17 +14947,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3456755</t>
+          <t>3529140</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3456755</t>
+          <t>3529140</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3456755</t>
+          <t>3529140</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -14982,17 +14982,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3658259</t>
+          <t>3730794</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3658259</t>
+          <t>3730794</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3658259</t>
+          <t>3730794</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15017,17 +15017,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>7115013</t>
+          <t>7259934</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>7115013</t>
+          <t>7259934</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7115013</t>
+          <t>7259934</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
